--- a/Tools/Signal_Timing_2026.xlsx
+++ b/Tools/Signal_Timing_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148C20A0-ACE5-4730-846C-B3FCE3345E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34665" yWindow="2040" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="2040" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
